--- a/docs/db/Garim_DB_Design_final_clean_v9.xlsx
+++ b/docs/db/Garim_DB_Design_final_clean_v9.xlsx
@@ -1053,7 +1053,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1289,107 +1289,95 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
-        <is>
-          <t>월 처리 한도</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>monthly_quota</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="n"/>
-      <c r="E8" s="17" t="n"/>
-      <c r="F8" s="17" t="n"/>
-      <c r="G8" s="17" t="n"/>
-      <c r="H8" s="17" t="n"/>
-      <c r="I8" s="17" t="inlineStr">
-        <is>
-          <t>월 처리 한도 정보를 저장하는 컬럼</t>
+      <c r="A8" s="20" t="inlineStr">
+        <is>
+          <t>배지 문구</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>badge_label</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>varchar(50)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="n"/>
+      <c r="E8" s="20" t="n"/>
+      <c r="F8" s="20" t="n"/>
+      <c r="G8" s="20" t="n"/>
+      <c r="H8" s="20" t="n"/>
+      <c r="I8" s="20" t="inlineStr">
+        <is>
+          <t>pricing 카드 상단 배지 문구. 예: 기본, 추천, 팀/스튜디오</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
-        <is>
-          <t>결과 보관 일수</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>result_retention_days</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="n"/>
-      <c r="E9" s="17" t="n"/>
-      <c r="F9" s="17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G9" s="17" t="n"/>
-      <c r="H9" s="17" t="n"/>
-      <c r="I9" s="17" t="inlineStr">
-        <is>
-          <t>결과 보관 일수 정보를 저장하는 컬럼</t>
+      <c r="A9" s="20" t="inlineStr">
+        <is>
+          <t>배지 스타일 클래스</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>badge_class</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>varchar(50)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="n"/>
+      <c r="E9" s="20" t="n"/>
+      <c r="F9" s="20" t="n"/>
+      <c r="G9" s="20" t="n"/>
+      <c r="H9" s="20" t="n"/>
+      <c r="I9" s="20" t="inlineStr">
+        <is>
+          <t>pricing 카드 배지 스타일 클래스. 예: mui-chip--primary</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="inlineStr">
-        <is>
-          <t>워터마크 포함 여부</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>watermark_required</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>boolean</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="n"/>
-      <c r="E10" s="17" t="n"/>
-      <c r="F10" s="17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G10" s="17" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="H10" s="17" t="n"/>
-      <c r="I10" s="17" t="inlineStr">
-        <is>
-          <t>워터마크 포함 여부 정보를 저장하는 컬럼</t>
+      <c r="A10" s="20" t="inlineStr">
+        <is>
+          <t>플랜 설명</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="n"/>
+      <c r="E10" s="20" t="n"/>
+      <c r="F10" s="20" t="n"/>
+      <c r="G10" s="20" t="n"/>
+      <c r="H10" s="20" t="n"/>
+      <c r="I10" s="20" t="inlineStr">
+        <is>
+          <t>pricing 카드 가격 아래 노출되는 플랜 소개 문구</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="17" t="inlineStr">
         <is>
-          <t>가격</t>
+          <t>월 처리 한도</t>
         </is>
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t>price_amount</t>
+          <t>monthly_quota</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr">
@@ -1399,41 +1387,29 @@
       </c>
       <c r="D11" s="17" t="n"/>
       <c r="E11" s="17" t="n"/>
-      <c r="F11" s="17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G11" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" s="17" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
-      </c>
+      <c r="F11" s="17" t="n"/>
+      <c r="G11" s="17" t="n"/>
+      <c r="H11" s="17" t="n"/>
       <c r="I11" s="17" t="inlineStr">
         <is>
-          <t>결제 또는 과금 계산에 사용하는 금액 값</t>
+          <t>월 처리 한도 정보를 저장하는 컬럼</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="17" t="inlineStr">
         <is>
-          <t>활성 여부</t>
+          <t>결과 보관 일수</t>
         </is>
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>is_active</t>
+          <t>result_retention_days</t>
         </is>
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D12" s="17" t="n"/>
@@ -1443,32 +1419,28 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G12" s="17" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
+      <c r="G12" s="17" t="n"/>
       <c r="H12" s="17" t="n"/>
       <c r="I12" s="17" t="inlineStr">
         <is>
-          <t>활성 여부 정보를 저장하는 컬럼</t>
+          <t>결과 보관 일수 정보를 저장하는 컬럼</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="17" t="inlineStr">
         <is>
-          <t>등록 일시</t>
+          <t>워터마크 포함 여부</t>
         </is>
       </c>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>watermark_required</t>
         </is>
       </c>
       <c r="C13" s="17" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="D13" s="17" t="n"/>
@@ -1480,171 +1452,346 @@
       </c>
       <c r="G13" s="17" t="inlineStr">
         <is>
-          <t>now()</t>
+          <t>true</t>
         </is>
       </c>
       <c r="H13" s="17" t="n"/>
       <c r="I13" s="17" t="inlineStr">
         <is>
+          <t>워터마크 포함 여부 정보를 저장하는 컬럼</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>가격</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>price_amount</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="D14" s="17" t="n"/>
+      <c r="E14" s="17" t="n"/>
+      <c r="F14" s="17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G14" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="17" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="I14" s="17" t="inlineStr">
+        <is>
+          <t>결제 또는 과금 계산에 사용하는 금액 값</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>정렬 순서</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>sort_order</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="n"/>
+      <c r="E15" s="20" t="n"/>
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G15" s="20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" s="20" t="n"/>
+      <c r="I15" s="20" t="inlineStr">
+        <is>
+          <t>pricing 페이지와 관리자 목록에 노출되는 순서</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="20" t="inlineStr">
+        <is>
+          <t>관리 상태</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>varchar(20)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="n"/>
+      <c r="E16" s="20" t="n"/>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G16" s="20" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="H16" s="20" t="inlineStr">
+        <is>
+          <t>active, inactive, deleted</t>
+        </is>
+      </c>
+      <c r="I16" s="20" t="inlineStr">
+        <is>
+          <t>플랜 관리 상태. 삭제는 row 삭제가 아니라 deleted 상태로 처리한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>등록 일시</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="D17" s="17" t="n"/>
+      <c r="E17" s="17" t="n"/>
+      <c r="F17" s="17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G17" s="17" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
+      <c r="H17" s="17" t="n"/>
+      <c r="I17" s="17" t="inlineStr">
+        <is>
           <t>레코드가 생성된 시각</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="20" t="inlineStr">
+        <is>
+          <t>수정 일시</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="n"/>
+      <c r="E18" s="20" t="n"/>
+      <c r="F18" s="20" t="n"/>
+      <c r="G18" s="20" t="n"/>
+      <c r="H18" s="20" t="n"/>
+      <c r="I18" s="20" t="inlineStr">
+        <is>
+          <t>레코드 마지막 수정 시각</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>최대 파일 크기 제한</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>file_size_limit</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>최대 파일 크기 제한 (MB 단위)</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>동시 처리 최대 건수</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>max_jobs</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>동시 처리 가능한 최대 작업 건수</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>원본 파일 자동 삭제 대기 시간</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>auto_delete_original_hours</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>원본 파일 자동 삭제 대기 시간 (시간 단위)</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>처리 메타데이터 보존 기간</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>metadata_retention_days</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>처리 메타데이터 보존 기간 (일 단위)</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>월 기본 제공 크레딧</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>credits</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>구독 플랜이 결제 또는 갱신 시 지급하는 기본 크레딧 수. 실제 잔액은 저장하지 않는다.</t>
         </is>
@@ -9576,7 +9723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I67"/>
+  <dimension ref="A1:I68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -11549,12 +11696,12 @@
     <row r="65">
       <c r="A65" s="22" t="inlineStr">
         <is>
-          <t>크레딧 상품 노출</t>
+          <t>구독 플랜 노출</t>
         </is>
       </c>
       <c r="B65" s="22" t="inlineStr">
         <is>
-          <t>idx_credit_plans_active_sort</t>
+          <t>idx_plans_active_status_sort</t>
         </is>
       </c>
       <c r="C65" s="22" t="inlineStr">
@@ -11568,24 +11715,24 @@
       <c r="G65" s="22" t="n"/>
       <c r="H65" s="22" t="inlineStr">
         <is>
-          <t>credit_plans(is_active, sort_order), 요금제 화면 노출</t>
+          <t>plans(is_active, status, sort_order), 요금제 화면 노출</t>
         </is>
       </c>
       <c r="I65" s="22" t="inlineStr">
         <is>
-          <t>활성 크레딧 상품을 정렬 순서로 조회</t>
+          <t>활성 상태의 구독 플랜을 관리 상태와 정렬 순서로 조회</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="22" t="inlineStr">
         <is>
-          <t>크레딧 원장 사용자 이력</t>
+          <t>크레딧 상품 노출</t>
         </is>
       </c>
       <c r="B66" s="22" t="inlineStr">
         <is>
-          <t>idx_credit_ledger_user_created_at</t>
+          <t>idx_credit_plans_active_status_sort</t>
         </is>
       </c>
       <c r="C66" s="22" t="inlineStr">
@@ -11594,33 +11741,29 @@
         </is>
       </c>
       <c r="D66" s="22" t="n"/>
-      <c r="E66" s="22" t="inlineStr">
-        <is>
-          <t>users.user_id</t>
-        </is>
-      </c>
+      <c r="E66" s="22" t="n"/>
       <c r="F66" s="22" t="n"/>
       <c r="G66" s="22" t="n"/>
       <c r="H66" s="22" t="inlineStr">
         <is>
-          <t>credit_ledger(user_id, created_at desc), 잔액 이력 조회</t>
+          <t>credit_plans(is_active, status, sort_order), 요금제 화면 노출</t>
         </is>
       </c>
       <c r="I66" s="22" t="inlineStr">
         <is>
-          <t>사용자별 최근 크레딧 변동 이력 조회</t>
+          <t>활성 상태의 크레딧 상품을 관리 상태와 정렬 순서로 조회</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="22" t="inlineStr">
         <is>
-          <t>결제 상품 유형 이력</t>
+          <t>크레딧 원장 사용자 이력</t>
         </is>
       </c>
       <c r="B67" s="22" t="inlineStr">
         <is>
-          <t>idx_payments_product_type_created_at</t>
+          <t>idx_credit_ledger_user_created_at</t>
         </is>
       </c>
       <c r="C67" s="22" t="inlineStr">
@@ -11629,15 +11772,50 @@
         </is>
       </c>
       <c r="D67" s="22" t="n"/>
-      <c r="E67" s="22" t="n"/>
+      <c r="E67" s="22" t="inlineStr">
+        <is>
+          <t>users.user_id</t>
+        </is>
+      </c>
       <c r="F67" s="22" t="n"/>
       <c r="G67" s="22" t="n"/>
       <c r="H67" s="22" t="inlineStr">
         <is>
+          <t>credit_ledger(user_id, created_at desc), 잔액 이력 조회</t>
+        </is>
+      </c>
+      <c r="I67" s="22" t="inlineStr">
+        <is>
+          <t>사용자별 최근 크레딧 변동 이력 조회</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="22" t="inlineStr">
+        <is>
+          <t>결제 상품 유형 이력</t>
+        </is>
+      </c>
+      <c r="B68" s="22" t="inlineStr">
+        <is>
+          <t>idx_payments_product_type_created_at</t>
+        </is>
+      </c>
+      <c r="C68" s="22" t="inlineStr">
+        <is>
+          <t>btree</t>
+        </is>
+      </c>
+      <c r="D68" s="22" t="n"/>
+      <c r="E68" s="22" t="n"/>
+      <c r="F68" s="22" t="n"/>
+      <c r="G68" s="22" t="n"/>
+      <c r="H68" s="22" t="inlineStr">
+        <is>
           <t>payments(product_type, created_at desc), 구독/크레딧 결제 분리 조회</t>
         </is>
       </c>
-      <c r="I67" s="22" t="inlineStr">
+      <c r="I68" s="22" t="inlineStr">
         <is>
           <t>상품 유형별 결제 이력 조회</t>
         </is>
@@ -14668,7 +14846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -14804,6 +14982,54 @@
       <c r="B11" s="26" t="inlineStr">
         <is>
           <t>Seeded credit_100 and credit_500 credit recharge products.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="26" t="inlineStr">
+        <is>
+          <t>Change 8</t>
+        </is>
+      </c>
+      <c r="B12" s="26" t="inlineStr">
+        <is>
+          <t>Added sort_order, status, and updated_at management fields for plans, added status for credit_plans, and aligned pricing display indexes with soft-delete filtering.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="26" t="inlineStr">
+        <is>
+          <t>Change 9</t>
+        </is>
+      </c>
+      <c r="B13" s="26" t="inlineStr">
+        <is>
+          <t>Added plans badge_label, badge_class, and description so pricing card copy can be managed by admin policy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Change 10</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Removed is_active and unified plan visibility logic to status column.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Change 11</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Removed cta_label from plans. Button text is now determined by static frontend rules.</t>
         </is>
       </c>
     </row>
@@ -15192,17 +15418,17 @@
     <row r="12">
       <c r="A12" s="26" t="inlineStr">
         <is>
-          <t>활성 여부</t>
+          <t>정렬 순서</t>
         </is>
       </c>
       <c r="B12" s="26" t="inlineStr">
         <is>
-          <t>is_active</t>
+          <t>sort_order</t>
         </is>
       </c>
       <c r="C12" s="26" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D12" s="26" t="n"/>
@@ -15214,30 +15440,30 @@
       </c>
       <c r="G12" s="26" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H12" s="26" t="n"/>
       <c r="I12" s="26" t="inlineStr">
         <is>
-          <t>구매 가능 여부</t>
+          <t>요금제 화면 노출 순서</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>정렬 순서</t>
+          <t>관리 상태</t>
         </is>
       </c>
       <c r="B13" s="26" t="inlineStr">
         <is>
-          <t>sort_order</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C13" s="26" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>varchar(20)</t>
         </is>
       </c>
       <c r="D13" s="26" t="n"/>
@@ -15249,13 +15475,17 @@
       </c>
       <c r="G13" s="26" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" s="26" t="n"/>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="H13" s="26" t="inlineStr">
+        <is>
+          <t>active, inactive, deleted</t>
+        </is>
+      </c>
       <c r="I13" s="26" t="inlineStr">
         <is>
-          <t>요금제 화면 노출 순서</t>
+          <t>크레딧 플랜 관리 상태. 삭제는 row 삭제가 아니라 deleted 상태로 처리한다.</t>
         </is>
       </c>
     </row>
